--- a/survey_templates/032_sports_club_member_experience_survey--survey_templates.xlsx
+++ b/survey_templates/032_sports_club_member_experience_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>programs</t>
+          <t>programs_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Programs</t>
+          <t>Programs 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>facilities_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Facilities 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>service_quality</t>
+          <t>service_quality_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Service Quality</t>
+          <t>Service Quality 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>member_experience</t>
+          <t>member_experience_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Member Experience</t>
+          <t>Member Experience 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Suggestions for Improvement</t>
+          <t>Member Suggestions For Improvement</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>programs</t>
+          <t>programs_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Programs</t>
+          <t>Programs 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>facilities_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Facilities 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1244,7 +1244,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>programs_choices</t>
+          <t>programs_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>programs_choices</t>
+          <t>programs_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>facilities_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>facilities_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1312,7 +1312,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>service_quality_choices</t>
+          <t>service_quality_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>service_quality_choices</t>
+          <t>service_quality_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1635,7 +1635,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>programs_choices</t>
+          <t>programs_3_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1652,7 +1652,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>programs_choices</t>
+          <t>programs_3_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1669,7 +1669,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>facilities_3_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1686,7 +1686,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>facilities_3_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
